--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,29 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AAA HACK CLUB PRJ\18. Path Finder\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3B5A9C-BB59-462F-998D-3B924E987F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Quanity</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Seeed Studio RP2040</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>JSTH 1x02 Connector</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005004955655144.html</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005011828090971.html</t>
+  </si>
+  <si>
+    <t>LEDs</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005005708510866.html</t>
+  </si>
+  <si>
+    <t>470 Resistor</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005002239656334.html</t>
+  </si>
+  <si>
+    <t>MX Switches</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/4000538042437.html</t>
+  </si>
+  <si>
+    <t>DSA KeyCaps</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/32842379355.html</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>JLC PCB</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -46,13 +153,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +444,153 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4">
+        <f>SUM(D2:D10)</f>
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{66C71F31-8AE8-40B4-AE5B-686FE5138CB0}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{876F3338-D9BD-4E0C-AB77-DDC777660C1F}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{83B9C773-9178-48CC-B173-38231CA17326}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{EE3EBB5A-39E4-4E3C-A351-F1092C69E64F}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{7DB4A0C7-879F-46E1-972D-C29EF6CAAF0A}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{84170FCF-E108-4890-9144-57EDD88BA81D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>